--- a/data.mn/public/datasets/registered-vehicles-by-province.xlsx
+++ b/data.mn/public/datasets/registered-vehicles-by-province.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,6 +416,11 @@
   </sheetPr>
   <dimension ref="A1:C309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -4451,6 +4456,11 @@
   </sheetPr>
   <dimension ref="A1:C309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
